--- a/calibration_plots/plot_data_vertebral_smpbart.xlsx
+++ b/calibration_plots/plot_data_vertebral_smpbart.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,41 +368,33 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.6606495726495727</v>
+        <v>0.6966410256410256</v>
       </c>
       <c r="B2">
-        <v>0.6923076923076923</v>
+        <v>0.6538461538461539</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.8654871794871795</v>
+        <v>0.9238076923076923</v>
       </c>
       <c r="B3">
-        <v>0.6410256410256411</v>
+        <v>0.7115384615384616</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.9619145299145299</v>
+        <v>0.9917254901960785</v>
       </c>
       <c r="B4">
-        <v>0.7948717948717948</v>
+        <v>0.8627450980392157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.9949298245614036</v>
+        <v>0.9999483870967741</v>
       </c>
       <c r="B5">
-        <v>0.8421052631578947</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>0.9999483870967741</v>
-      </c>
-      <c r="B6">
         <v>0.9870967741935484</v>
       </c>
     </row>
